--- a/data-source/不可升级建筑数据.xlsx
+++ b/data-source/不可升级建筑数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0808E49-525D-4DB0-84BE-2D3F30D6E5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95738F0-2591-40A0-B4CC-473823F5587F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{345D919C-BD97-4FB0-A520-39D64B4D9066}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="207">
   <si>
     <t>建筑名称</t>
   </si>
@@ -651,6 +651,15 @@
   </si>
   <si>
     <t>宝箱的价格无法与内容物的价值相提并论，仅第一二季红猎出现过</t>
+  </si>
+  <si>
+    <t>击剑假人</t>
+  </si>
+  <si>
+    <t>红猎</t>
+  </si>
+  <si>
+    <t>和营地的假人异曲同工，用来测试武器效果，不消耗耐久，和营地不同的是，击剑假人的储存栏位中可放置被击败敌人的头颅，它将获得原持有者的防御属性</t>
   </si>
 </sst>
 </file>
@@ -723,11 +732,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thick">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
+      <top style="thick">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -736,7 +745,7 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
+      <top style="thick">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -744,17 +753,17 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right style="thick">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thick">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thick">
         <color indexed="64"/>
       </left>
       <right/>
@@ -764,7 +773,7 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right style="thick">
         <color indexed="64"/>
       </right>
       <top/>
@@ -772,12 +781,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thick">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -786,18 +795,18 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right style="thick">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -806,10 +815,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -826,9 +841,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -841,11 +853,17 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1196,32 +1214,32 @@
     <col min="9" max="9" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:19" ht="13.9" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J1" s="1"/>
@@ -1235,31 +1253,31 @@
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>5</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>10</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>95</v>
       </c>
       <c r="J2" s="1"/>
@@ -1273,29 +1291,29 @@
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1">
-        <v>200</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="7">
+      <c r="B3" s="2">
+        <v>200</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="8" t="s">
         <v>97</v>
       </c>
       <c r="J3" s="1"/>
@@ -1309,29 +1327,29 @@
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>150</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J4" s="1"/>
@@ -1345,29 +1363,29 @@
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>10</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="G5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J5" s="1"/>
@@ -1381,29 +1399,29 @@
       <c r="R5" s="1"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>50</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2">
         <v>2</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="G6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J6" s="1"/>
@@ -1417,29 +1435,29 @@
       <c r="R6" s="1"/>
     </row>
     <row r="7" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>1500</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="8" t="s">
         <v>97</v>
       </c>
       <c r="J7" s="1"/>
@@ -1453,31 +1471,31 @@
       <c r="R7" s="1"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>20</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="2">
         <v>15</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="2">
         <v>100</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="G8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="8" t="s">
         <v>95</v>
       </c>
       <c r="J8" s="1"/>
@@ -1492,29 +1510,29 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
         <v>100</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2">
         <v>2</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="G9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J9" s="1"/>
@@ -1529,29 +1547,29 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2">
         <v>100</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
         <v>2</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="G10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J10" s="1"/>
@@ -1566,29 +1584,29 @@
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>100</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="G11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J11" s="1"/>
@@ -1603,29 +1621,29 @@
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19" ht="54" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="2">
         <v>0</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
         <v>80</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="G12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J12" s="1"/>
@@ -1640,29 +1658,29 @@
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="1">
-        <v>200</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
+      <c r="B13" s="2">
+        <v>200</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2">
         <v>2</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="G13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J13" s="1"/>
@@ -1677,29 +1695,29 @@
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>1000</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="8" t="s">
         <v>97</v>
       </c>
       <c r="J14" s="1"/>
@@ -1714,29 +1732,29 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <v>50</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2">
         <v>10</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="1" t="s">
+      <c r="G15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J15" s="1"/>
@@ -1751,29 +1769,29 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="1">
-        <v>200</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
+      <c r="B16" s="2">
+        <v>200</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2">
         <v>1</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="1" t="s">
+      <c r="G16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J16" s="1"/>
@@ -1788,29 +1806,29 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="1">
-        <v>200</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
+      <c r="B17" s="2">
+        <v>200</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2">
         <v>3</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="1" t="s">
+      <c r="G17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J17" s="1"/>
@@ -1825,31 +1843,31 @@
       <c r="S17" s="1"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="2">
         <v>50</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2">
         <v>20</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="2">
         <v>100</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="G18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="8" t="s">
         <v>95</v>
       </c>
       <c r="J18" s="1"/>
@@ -1864,29 +1882,29 @@
       <c r="S18" s="1"/>
     </row>
     <row r="19" spans="1:19" ht="94.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="2">
         <v>1000</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="8" t="s">
         <v>97</v>
       </c>
       <c r="J19" s="1"/>
@@ -1901,29 +1919,29 @@
       <c r="S19" s="1"/>
     </row>
     <row r="20" spans="1:19" ht="108" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="2">
         <v>1500</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1">
+      <c r="C20" s="2"/>
+      <c r="D20" s="2">
         <v>1</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="8" t="s">
         <v>97</v>
       </c>
       <c r="J20" s="1"/>
@@ -1938,29 +1956,29 @@
       <c r="S20" s="1"/>
     </row>
     <row r="21" spans="1:19" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2">
         <v>2000</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2">
         <v>1</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="8" t="s">
         <v>97</v>
       </c>
       <c r="J21" s="1"/>
@@ -1975,29 +1993,29 @@
       <c r="S21" s="1"/>
     </row>
     <row r="22" spans="1:19" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="2">
         <v>100</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1">
+      <c r="C22" s="2"/>
+      <c r="D22" s="2">
         <v>8</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="G22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J22" s="1"/>
@@ -2012,31 +2030,31 @@
       <c r="S22" s="1"/>
     </row>
     <row r="23" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="1">
-        <v>200</v>
-      </c>
-      <c r="C23" s="1">
+      <c r="B23" s="2">
+        <v>200</v>
+      </c>
+      <c r="C23" s="2">
         <v>10</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="2">
         <v>100</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="6" t="s">
+      <c r="F23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="8" t="s">
         <v>102</v>
       </c>
       <c r="J23" s="1"/>
@@ -2051,31 +2069,31 @@
       <c r="S23" s="1"/>
     </row>
     <row r="24" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="1">
-        <v>200</v>
-      </c>
-      <c r="C24" s="1">
+      <c r="B24" s="2">
+        <v>200</v>
+      </c>
+      <c r="C24" s="2">
         <v>10</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="2">
         <v>3</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" s="1" t="s">
+      <c r="G24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J24" s="1"/>
@@ -2090,31 +2108,31 @@
       <c r="S24" s="1"/>
     </row>
     <row r="25" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="2">
         <v>300</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="2">
         <v>8</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="2">
         <v>999</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="6" t="s">
+      <c r="F25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>102</v>
       </c>
       <c r="J25" s="1"/>
@@ -2129,31 +2147,31 @@
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="2">
         <v>300</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="2">
         <v>6</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="2">
         <v>2</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="1" t="s">
+      <c r="G26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="8" t="s">
         <v>96</v>
       </c>
       <c r="J26" s="1"/>
@@ -2168,29 +2186,29 @@
       <c r="S26" s="1"/>
     </row>
     <row r="27" spans="1:19" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="2">
         <v>2000</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2">
         <v>2</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="8" t="s">
         <v>97</v>
       </c>
       <c r="J27" s="1"/>
@@ -2205,1202 +2223,1220 @@
       <c r="S27" s="1"/>
     </row>
     <row r="28" spans="1:19" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="2">
         <v>2000</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2">
         <v>1</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="8" t="s">
         <v>97</v>
       </c>
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="2">
         <v>600</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2">
         <v>50</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="6" t="s">
+      <c r="F29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="8" t="s">
         <v>100</v>
       </c>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:19" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="2">
         <v>100</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2">
         <v>5</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="G30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="8" t="s">
         <v>106</v>
       </c>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="2">
         <v>50</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2">
         <v>3</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="G31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="8" t="s">
         <v>110</v>
       </c>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="2">
         <v>500</v>
       </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1">
+      <c r="C32" s="2"/>
+      <c r="D32" s="2">
         <v>50</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" s="6" t="s">
+      <c r="F32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="8" t="s">
         <v>102</v>
       </c>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="2">
         <v>500</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1">
+      <c r="C33" s="2"/>
+      <c r="D33" s="2">
         <v>30</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="6" t="s">
+      <c r="F33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>102</v>
       </c>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="2">
         <v>500</v>
       </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1">
+      <c r="C34" s="2"/>
+      <c r="D34" s="2">
         <v>50</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="6" t="s">
+      <c r="F34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="8" t="s">
         <v>102</v>
       </c>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B35" s="1">
-        <v>200</v>
-      </c>
-      <c r="C35" s="1">
+      <c r="B35" s="2">
+        <v>200</v>
+      </c>
+      <c r="C35" s="2">
         <v>20</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="2">
         <v>999</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" s="6" t="s">
+      <c r="F35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="8" t="s">
         <v>189</v>
       </c>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B36" s="1">
-        <v>200</v>
-      </c>
-      <c r="C36" s="1">
+      <c r="B36" s="2">
+        <v>200</v>
+      </c>
+      <c r="C36" s="2">
         <v>20</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="2">
         <v>999</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" s="10" t="s">
+      <c r="F36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="11" t="s">
         <v>189</v>
       </c>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B37" s="1">
-        <v>200</v>
-      </c>
-      <c r="C37" s="1">
+      <c r="B37" s="2">
+        <v>200</v>
+      </c>
+      <c r="C37" s="2">
         <v>20</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="2">
         <v>999</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" s="10" t="s">
+      <c r="F37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="11" t="s">
         <v>189</v>
       </c>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B38" s="1">
-        <v>200</v>
-      </c>
-      <c r="C38" s="1">
+      <c r="B38" s="2">
+        <v>200</v>
+      </c>
+      <c r="C38" s="2">
         <v>20</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="2">
         <v>999</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="10" t="s">
+      <c r="F38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="11" t="s">
         <v>190</v>
       </c>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="1">
-        <v>200</v>
-      </c>
-      <c r="C39" s="1">
+      <c r="B39" s="2">
+        <v>200</v>
+      </c>
+      <c r="C39" s="2">
         <v>20</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="2">
         <v>999</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" s="10" t="s">
+      <c r="F39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="11" t="s">
         <v>190</v>
       </c>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B40" s="1">
-        <v>200</v>
-      </c>
-      <c r="C40" s="1">
+      <c r="B40" s="2">
+        <v>200</v>
+      </c>
+      <c r="C40" s="2">
         <v>20</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="2">
         <v>999</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" s="10" t="s">
+      <c r="F40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="11" t="s">
         <v>191</v>
       </c>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B41" s="1">
-        <v>200</v>
-      </c>
-      <c r="C41" s="1">
+      <c r="B41" s="2">
+        <v>200</v>
+      </c>
+      <c r="C41" s="2">
         <v>20</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="2">
         <v>999</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="10" t="s">
+      <c r="F41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="11" t="s">
         <v>202</v>
       </c>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="1">
-        <v>200</v>
-      </c>
-      <c r="C42" s="1">
+      <c r="B42" s="2">
+        <v>200</v>
+      </c>
+      <c r="C42" s="2">
         <v>25</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="2">
         <v>999</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="10" t="s">
+      <c r="F42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="11" t="s">
         <v>192</v>
       </c>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B43" s="1">
-        <v>200</v>
-      </c>
-      <c r="C43" s="1">
+      <c r="B43" s="2">
+        <v>200</v>
+      </c>
+      <c r="C43" s="2">
         <v>25</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="2">
         <v>999</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" s="10" t="s">
+      <c r="F43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="11" t="s">
         <v>189</v>
       </c>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B44" s="1">
-        <v>200</v>
-      </c>
-      <c r="C44" s="1">
+      <c r="B44" s="2">
+        <v>200</v>
+      </c>
+      <c r="C44" s="2">
         <v>25</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="2">
         <v>999</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="10" t="s">
+      <c r="F44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="11" t="s">
         <v>189</v>
       </c>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B45" s="1">
-        <v>200</v>
-      </c>
-      <c r="C45" s="1">
+      <c r="B45" s="2">
+        <v>200</v>
+      </c>
+      <c r="C45" s="2">
         <v>25</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="2">
         <v>999</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="10" t="s">
+      <c r="F45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" s="11" t="s">
         <v>189</v>
       </c>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="2">
         <v>300</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="2">
         <v>25</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="2">
         <v>999</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="10" t="s">
+      <c r="F46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="11" t="s">
         <v>193</v>
       </c>
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="1">
-        <v>200</v>
-      </c>
-      <c r="C47" s="1">
+      <c r="B47" s="2">
+        <v>200</v>
+      </c>
+      <c r="C47" s="2">
         <v>25</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="2">
         <v>999</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I47" s="10" t="s">
+      <c r="F47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" s="11" t="s">
         <v>190</v>
       </c>
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B48" s="1">
-        <v>200</v>
-      </c>
-      <c r="C48" s="1">
+      <c r="B48" s="2">
+        <v>200</v>
+      </c>
+      <c r="C48" s="2">
         <v>25</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="2">
         <v>999</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I48" s="10" t="s">
+      <c r="F48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" s="11" t="s">
         <v>191</v>
       </c>
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B49" s="1">
-        <v>200</v>
-      </c>
-      <c r="C49" s="1">
+      <c r="B49" s="2">
+        <v>200</v>
+      </c>
+      <c r="C49" s="2">
         <v>25</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="2">
         <v>999</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" s="10" t="s">
+      <c r="F49" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" s="11" t="s">
         <v>191</v>
       </c>
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B50" s="1">
-        <v>200</v>
-      </c>
-      <c r="C50" s="1">
+      <c r="B50" s="2">
+        <v>200</v>
+      </c>
+      <c r="C50" s="2">
         <v>30</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="2">
         <v>999</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I50" s="10" t="s">
+      <c r="F50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" s="11" t="s">
         <v>189</v>
       </c>
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="B51" s="1">
-        <v>200</v>
-      </c>
-      <c r="C51" s="1">
+      <c r="B51" s="2">
+        <v>200</v>
+      </c>
+      <c r="C51" s="2">
         <v>30</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" s="2">
         <v>999</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I51" s="10" t="s">
+      <c r="F51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="11" t="s">
         <v>194</v>
       </c>
       <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B52" s="1">
-        <v>200</v>
-      </c>
-      <c r="C52" s="1">
+      <c r="B52" s="2">
+        <v>200</v>
+      </c>
+      <c r="C52" s="2">
         <v>30</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D52" s="2">
         <v>999</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I52" s="10" t="s">
+      <c r="F52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="11" t="s">
         <v>189</v>
       </c>
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B53" s="1">
-        <v>200</v>
-      </c>
-      <c r="C53" s="1">
+      <c r="B53" s="2">
+        <v>200</v>
+      </c>
+      <c r="C53" s="2">
         <v>30</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="2">
         <v>999</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" s="10" t="s">
+      <c r="F53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="11" t="s">
         <v>189</v>
       </c>
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B54" s="1">
-        <v>200</v>
-      </c>
-      <c r="C54" s="1">
+      <c r="B54" s="2">
+        <v>200</v>
+      </c>
+      <c r="C54" s="2">
         <v>30</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" s="2">
         <v>999</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" s="10" t="s">
+      <c r="F54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="11" t="s">
         <v>195</v>
       </c>
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B55" s="1">
-        <v>200</v>
-      </c>
-      <c r="C55" s="1">
+      <c r="B55" s="2">
+        <v>200</v>
+      </c>
+      <c r="C55" s="2">
         <v>30</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="2">
         <v>999</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I55" s="10" t="s">
+      <c r="F55" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="11" t="s">
         <v>196</v>
       </c>
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B56" s="1">
-        <v>200</v>
-      </c>
-      <c r="C56" s="1">
+      <c r="B56" s="2">
+        <v>200</v>
+      </c>
+      <c r="C56" s="2">
         <v>30</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="2">
         <v>999</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I56" s="10" t="s">
+      <c r="F56" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="11" t="s">
         <v>195</v>
       </c>
       <c r="J56" s="1"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B57" s="1">
-        <v>200</v>
-      </c>
-      <c r="C57" s="1">
+      <c r="B57" s="2">
+        <v>200</v>
+      </c>
+      <c r="C57" s="2">
         <v>30</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="2">
         <v>999</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I57" s="10" t="s">
+      <c r="F57" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="11" t="s">
         <v>197</v>
       </c>
       <c r="J57" s="1"/>
     </row>
     <row r="58" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B58" s="1">
-        <v>200</v>
-      </c>
-      <c r="C58" s="1">
+      <c r="B58" s="2">
+        <v>200</v>
+      </c>
+      <c r="C58" s="2">
         <v>30</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="2">
         <v>999</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I58" s="10" t="s">
+      <c r="F58" s="2"/>
+      <c r="G58" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" s="11" t="s">
         <v>190</v>
       </c>
       <c r="J58" s="1"/>
     </row>
     <row r="59" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B59" s="1">
-        <v>200</v>
-      </c>
-      <c r="C59" s="1">
+      <c r="B59" s="2">
+        <v>200</v>
+      </c>
+      <c r="C59" s="2">
         <v>30</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="2">
         <v>999</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I59" s="10" t="s">
+      <c r="F59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="11" t="s">
         <v>191</v>
       </c>
       <c r="J59" s="1"/>
     </row>
     <row r="60" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B60" s="1">
-        <v>200</v>
-      </c>
-      <c r="C60" s="1">
+      <c r="B60" s="2">
+        <v>200</v>
+      </c>
+      <c r="C60" s="2">
         <v>30</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" s="2">
         <v>999</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I60" s="10" t="s">
+      <c r="F60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="11" t="s">
         <v>191</v>
       </c>
       <c r="J60" s="1"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B61" s="1">
-        <v>200</v>
-      </c>
-      <c r="C61" s="1">
+      <c r="B61" s="2">
+        <v>200</v>
+      </c>
+      <c r="C61" s="2">
         <v>35</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D61" s="2">
         <v>999</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I61" s="10" t="s">
+      <c r="F61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" s="11" t="s">
         <v>195</v>
       </c>
       <c r="J61" s="1"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B62" s="1">
-        <v>200</v>
-      </c>
-      <c r="C62" s="1">
+      <c r="B62" s="2">
+        <v>200</v>
+      </c>
+      <c r="C62" s="2">
         <v>35</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D62" s="2">
         <v>999</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I62" s="10" t="s">
+      <c r="F62" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I62" s="11" t="s">
         <v>195</v>
       </c>
       <c r="J62" s="1"/>
     </row>
     <row r="63" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B63" s="1">
-        <v>200</v>
-      </c>
-      <c r="C63" s="1">
+      <c r="B63" s="2">
+        <v>200</v>
+      </c>
+      <c r="C63" s="2">
         <v>35</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D63" s="2">
         <v>999</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I63" s="10" t="s">
+      <c r="F63" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I63" s="11" t="s">
         <v>198</v>
       </c>
       <c r="J63" s="1"/>
     </row>
     <row r="64" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B64" s="1">
-        <v>200</v>
-      </c>
-      <c r="C64" s="1">
+      <c r="B64" s="2">
+        <v>200</v>
+      </c>
+      <c r="C64" s="2">
         <v>35</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" s="2">
         <v>999</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I64" s="10" t="s">
+      <c r="F64" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I64" s="11" t="s">
         <v>190</v>
       </c>
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B65" s="1">
-        <v>200</v>
-      </c>
-      <c r="C65" s="1">
+      <c r="B65" s="2">
+        <v>200</v>
+      </c>
+      <c r="C65" s="2">
         <v>35</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="2">
         <v>999</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I65" s="10" t="s">
+      <c r="F65" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" s="11" t="s">
         <v>191</v>
       </c>
       <c r="J65" s="1"/>
     </row>
     <row r="66" spans="1:10" ht="27" x14ac:dyDescent="0.3">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B66" s="1">
-        <v>200</v>
-      </c>
-      <c r="C66" s="1">
+      <c r="B66" s="2">
+        <v>200</v>
+      </c>
+      <c r="C66" s="2">
         <v>40</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D66" s="2">
         <v>999</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I66" s="10" t="s">
+      <c r="F66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" s="11" t="s">
         <v>191</v>
       </c>
       <c r="J66" s="1"/>
     </row>
-    <row r="67" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="12" t="s">
+    <row r="67" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="A67" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="B67" s="13">
-        <v>200</v>
-      </c>
-      <c r="C67" s="13">
+      <c r="B67" s="2">
+        <v>200</v>
+      </c>
+      <c r="C67" s="2">
         <v>50</v>
       </c>
-      <c r="D67" s="13">
+      <c r="D67" s="2">
         <v>999</v>
       </c>
-      <c r="E67" s="13" t="s">
+      <c r="E67" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F67" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G67" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H67" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I67" s="14" t="s">
+      <c r="F67" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" s="11" t="s">
         <v>199</v>
       </c>
       <c r="J67" s="1"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
+    <row r="68" spans="1:10" ht="54.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B68" s="15">
+        <v>200</v>
+      </c>
+      <c r="C68" s="15">
+        <v>1</v>
+      </c>
+      <c r="D68" s="15">
+        <v>999</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="17" t="s">
+        <v>205</v>
+      </c>
       <c r="J68" s="1"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="13.9" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3473,6 +3509,15 @@
       <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">

--- a/data-source/不可升级建筑数据.xlsx
+++ b/data-source/不可升级建筑数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB83B54-084D-4076-A9D1-B1345CF6A106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11B4029-EB63-4F54-BFAC-AEDE6F73D2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{345D919C-BD97-4FB0-A520-39D64B4D9066}"/>
   </bookViews>
@@ -650,7 +650,7 @@
     <t>红猎</t>
   </si>
   <si>
-    <t>和营地的假人异曲同工，用来测试武器效果，不消耗耐久，和营地不同的是，击剑假人的储存栏位中可放置被击败敌人的头颅，它将获得原持有者的防御属性</t>
+    <t>和营地的假人异曲同工，用来测试武器效果，不消耗耐久，和营地不同的是，击剑假人的储存栏位中可放置被击败敌人的头颅，它将获得原持有者的防御属性，但是，经过测试，假人目前8.5.0版本中不吃穿甲，用战锤打boss继母艾莎为44，但是打假人为26，用战锤打罗格沃尔boss为80，打假人为61，可见假人目前不吃穿甲，且所有弓箭打假人艾莎均有伤害，但是实际boss战中弓箭无法对艾莎造成伤害</t>
   </si>
 </sst>
 </file>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="J66" s="1"/>
     </row>
-    <row r="67" spans="1:10" ht="54.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" ht="121.9" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="13" t="s">
         <v>201</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="14">
-        <v>999</v>
+        <v>8</v>
       </c>
       <c r="E67" s="15" t="s">
         <v>203</v>
